--- a/entorno/mir-v2/archivos_de_prueba/Chaco_correctos/MPJ_DAE_2026_T1_Chaco.xlsx
+++ b/entorno/mir-v2/archivos_de_prueba/Chaco_correctos/MPJ_DAE_2026_T1_Chaco.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="MPJ" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="DAE" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="INSTRUCCIONES" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="LISTAS" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MPJ" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DAE" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INSTRUCCIONES" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTAS" sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/entorno/mir-v2/archivos_de_prueba/Chaco_correctos/MPJ_DAE_2026_T1_Chaco.xlsx
+++ b/entorno/mir-v2/archivos_de_prueba/Chaco_correctos/MPJ_DAE_2026_T1_Chaco.xlsx
@@ -267,7 +267,7 @@
         <t>ID del Niño, niña o Adolescente
 Identificador alfanumérico nominal único provincial asignado al NyA para seguimiento resguardando su identidad. En caso de existir.
 Qué se espera: un número entero
-No es obligatorio.</t>
+Campo obligatorio.</t>
       </text>
     </comment>
     <comment ref="H3" authorId="0" shapeId="0">
@@ -623,7 +623,7 @@
       <text>
         <t>ID del Niño, niña o Adolescente
 Qué se espera: un número entero
-No es obligatorio.</t>
+Campo obligatorio.</t>
       </text>
     </comment>
     <comment ref="H3" authorId="0" shapeId="0">
@@ -1323,9 +1323,9 @@
           <t>Localidad</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>ID del Niño, niña o Adolescente</t>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>ID del Niño, niña o Adolescente *</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -1486,7 +1486,7 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
-        <v>45632</v>
+        <v>45633</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="AC4" s="5" t="n">
-        <v>45683</v>
+        <v>45684</v>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>42.84</v>
       </c>
       <c r="AI4" s="5" t="n">
-        <v>45755</v>
+        <v>45756</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="AC5" s="5" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>29.65</v>
       </c>
       <c r="AI5" s="5" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="AC6" s="5" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>27.51</v>
       </c>
       <c r="AI6" s="5" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>46069</v>
+        <v>46070</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         </is>
       </c>
       <c r="AC7" s="5" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>68.37</v>
       </c>
       <c r="AI7" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
-        <v>45676</v>
+        <v>45677</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="AC8" s="5" t="n">
-        <v>45632</v>
+        <v>45633</v>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>38.02</v>
       </c>
       <c r="AI8" s="5" t="n">
-        <v>45674</v>
+        <v>45675</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
-        <v>45673</v>
+        <v>45674</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         </is>
       </c>
       <c r="AC9" s="5" t="n">
-        <v>45853</v>
+        <v>45854</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>31.86</v>
       </c>
       <c r="AI9" s="5" t="n">
-        <v>46025</v>
+        <v>46026</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
-        <v>45824</v>
+        <v>45825</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="AC10" s="5" t="n">
-        <v>45789</v>
+        <v>45790</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>93.62</v>
       </c>
       <c r="AI10" s="5" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>45802</v>
+        <v>45803</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         </is>
       </c>
       <c r="AC11" s="5" t="n">
-        <v>45737</v>
+        <v>45738</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>28.58</v>
       </c>
       <c r="AI11" s="5" t="n">
-        <v>45801</v>
+        <v>45802</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="AC12" s="5" t="n">
-        <v>45983</v>
+        <v>45984</v>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>54.68</v>
       </c>
       <c r="AI12" s="5" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
-        <v>45688</v>
+        <v>45689</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         </is>
       </c>
       <c r="AC13" s="5" t="n">
-        <v>45601</v>
+        <v>45602</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>13.96</v>
       </c>
       <c r="AI13" s="5" t="n">
-        <v>45767</v>
+        <v>45768</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         </is>
       </c>
       <c r="AC14" s="5" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>12.43</v>
       </c>
       <c r="AI14" s="5" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
-        <v>45998</v>
+        <v>45999</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         </is>
       </c>
       <c r="AC15" s="5" t="n">
-        <v>45834</v>
+        <v>45835</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>1.96</v>
       </c>
       <c r="AI15" s="5" t="n">
-        <v>45854</v>
+        <v>45855</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
-        <v>45908</v>
+        <v>45909</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="AC16" s="5" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
         <v>93.15000000000001</v>
       </c>
       <c r="AI16" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
         </is>
       </c>
       <c r="AC17" s="5" t="n">
-        <v>45947</v>
+        <v>45948</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>58.48</v>
       </c>
       <c r="AI17" s="5" t="n">
-        <v>46015</v>
+        <v>46016</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
-        <v>45842</v>
+        <v>45843</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         </is>
       </c>
       <c r="AC18" s="5" t="n">
-        <v>45607</v>
+        <v>45608</v>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>31.62</v>
       </c>
       <c r="AI18" s="5" t="n">
-        <v>45712</v>
+        <v>45713</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
-        <v>45984</v>
+        <v>45985</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         </is>
       </c>
       <c r="AC19" s="5" t="n">
-        <v>45834</v>
+        <v>45835</v>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>79.58</v>
       </c>
       <c r="AI19" s="5" t="n">
-        <v>46023</v>
+        <v>46024</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
-        <v>45996</v>
+        <v>45997</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         </is>
       </c>
       <c r="AC20" s="5" t="n">
-        <v>45615</v>
+        <v>45616</v>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>18.41</v>
       </c>
       <c r="AI20" s="5" t="n">
-        <v>45794</v>
+        <v>45795</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
-        <v>45716</v>
+        <v>45717</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         </is>
       </c>
       <c r="AC21" s="5" t="n">
-        <v>45645</v>
+        <v>45646</v>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>71.64</v>
       </c>
       <c r="AI21" s="5" t="n">
-        <v>45706</v>
+        <v>45707</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
-        <v>45733</v>
+        <v>45734</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="AC22" s="5" t="n">
-        <v>45798</v>
+        <v>45799</v>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>39.61</v>
       </c>
       <c r="AI22" s="5" t="n">
-        <v>45906</v>
+        <v>45907</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
-        <v>45727</v>
+        <v>45728</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -4777,7 +4777,7 @@
         </is>
       </c>
       <c r="AC23" s="5" t="n">
-        <v>45848</v>
+        <v>45849</v>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
@@ -4799,7 +4799,7 @@
         <v>26.76</v>
       </c>
       <c r="AI23" s="5" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>45941</v>
+        <v>45942</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="AC24" s="5" t="n">
-        <v>45802</v>
+        <v>45803</v>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
@@ -4961,7 +4961,7 @@
         <v>47.04</v>
       </c>
       <c r="AI24" s="5" t="n">
-        <v>45868</v>
+        <v>45869</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -4977,7 +4977,7 @@
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
-        <v>45665</v>
+        <v>45666</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="AC25" s="5" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>85.11</v>
       </c>
       <c r="AI25" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
-        <v>45636</v>
+        <v>45637</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         </is>
       </c>
       <c r="AC26" s="5" t="n">
-        <v>45811</v>
+        <v>45812</v>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>3.84</v>
       </c>
       <c r="AI26" s="5" t="n">
-        <v>45895</v>
+        <v>45896</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="AC27" s="5" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         <v>47.85</v>
       </c>
       <c r="AI27" s="5" t="n">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
-        <v>45723</v>
+        <v>45724</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -5596,7 +5596,7 @@
         </is>
       </c>
       <c r="AC28" s="5" t="n">
-        <v>45983</v>
+        <v>45984</v>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
@@ -5618,7 +5618,7 @@
         <v>2.4</v>
       </c>
       <c r="AI28" s="5" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="AC29" s="5" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>15.77</v>
       </c>
       <c r="AI29" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         </is>
       </c>
       <c r="AC30" s="5" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         <v>8.43</v>
       </c>
       <c r="AI30" s="5" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
-        <v>45678</v>
+        <v>45679</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -6093,7 +6093,7 @@
         </is>
       </c>
       <c r="AC31" s="5" t="n">
-        <v>46213</v>
+        <v>46214</v>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>75.15000000000001</v>
       </c>
       <c r="AI31" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
-        <v>45807</v>
+        <v>45808</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -6259,7 +6259,7 @@
         </is>
       </c>
       <c r="AC32" s="5" t="n">
-        <v>45619</v>
+        <v>45620</v>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>44.15</v>
       </c>
       <c r="AI32" s="5" t="n">
-        <v>45745</v>
+        <v>45746</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
-        <v>45868</v>
+        <v>45869</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         </is>
       </c>
       <c r="AC33" s="5" t="n">
-        <v>45813</v>
+        <v>45814</v>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
         <v>36.82</v>
       </c>
       <c r="AI33" s="5" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -8162,9 +8162,9 @@
           <t>Localidad</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>ID del Niño, niña o Adolescente</t>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>ID del Niño, niña o Adolescente *</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -8350,7 +8350,7 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -8473,7 +8473,7 @@
         </is>
       </c>
       <c r="AC4" s="5" t="n">
-        <v>46129</v>
+        <v>46130</v>
       </c>
       <c r="AD4" s="8" t="n">
         <v>0.8958333333333334</v>
@@ -8504,7 +8504,7 @@
         </is>
       </c>
       <c r="AJ4" s="5" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="AK4" s="8" t="n">
         <v>0.96875</v>
@@ -8532,7 +8532,7 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         </is>
       </c>
       <c r="AC5" s="5" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="AD5" s="8" t="n">
         <v>0.7604166666666666</v>
@@ -8690,7 +8690,7 @@
         </is>
       </c>
       <c r="AJ5" s="5" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="AK5" s="8" t="n">
         <v>0.78125</v>
@@ -8722,7 +8722,7 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>45947</v>
+        <v>45948</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         </is>
       </c>
       <c r="AC6" s="5" t="n">
-        <v>45645</v>
+        <v>45646</v>
       </c>
       <c r="AD6" s="8" t="n">
         <v>0.875</v>
@@ -8880,7 +8880,7 @@
         </is>
       </c>
       <c r="AJ6" s="5" t="n">
-        <v>45669</v>
+        <v>45670</v>
       </c>
       <c r="AK6" s="8" t="n">
         <v>0.7916666666666666</v>
@@ -8908,7 +8908,7 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
         </is>
       </c>
       <c r="AC7" s="5" t="n">
-        <v>45814</v>
+        <v>45815</v>
       </c>
       <c r="AD7" s="8" t="n">
         <v>0.6145833333333334</v>
@@ -9066,7 +9066,7 @@
         </is>
       </c>
       <c r="AJ7" s="5" t="n">
-        <v>45954</v>
+        <v>45955</v>
       </c>
       <c r="AK7" s="8" t="n">
         <v>0.4583333333333333</v>
@@ -9094,7 +9094,7 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         </is>
       </c>
       <c r="AC8" s="5" t="n">
-        <v>45778</v>
+        <v>45779</v>
       </c>
       <c r="AD8" s="8" t="n">
         <v>0.6354166666666666</v>
@@ -9257,7 +9257,7 @@
         </is>
       </c>
       <c r="AJ8" s="5" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="AK8" s="8" t="n">
         <v>0.4166666666666667</v>
@@ -9285,7 +9285,7 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
         </is>
       </c>
       <c r="AC9" s="5" t="n">
-        <v>45594</v>
+        <v>45595</v>
       </c>
       <c r="AD9" s="8" t="n">
         <v>0.7708333333333334</v>
@@ -9439,7 +9439,7 @@
         </is>
       </c>
       <c r="AJ9" s="5" t="n">
-        <v>45626</v>
+        <v>45627</v>
       </c>
       <c r="AK9" s="8" t="n">
         <v>0.8541666666666666</v>
@@ -9475,7 +9475,7 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -9598,7 +9598,7 @@
         </is>
       </c>
       <c r="AC10" s="5" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="AD10" s="8" t="n">
         <v>0.78125</v>
@@ -9629,7 +9629,7 @@
         </is>
       </c>
       <c r="AJ10" s="5" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="AK10" s="8" t="n">
         <v>0.7916666666666666</v>
@@ -9665,7 +9665,7 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -9797,7 +9797,7 @@
         </is>
       </c>
       <c r="AC11" s="5" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="AD11" s="8" t="n">
         <v>0.4270833333333333</v>
@@ -9828,7 +9828,7 @@
         </is>
       </c>
       <c r="AJ11" s="5" t="n">
-        <v>46122</v>
+        <v>46123</v>
       </c>
       <c r="AK11" s="8" t="n">
         <v>0.4166666666666667</v>
@@ -9856,7 +9856,7 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -9979,7 +9979,7 @@
         </is>
       </c>
       <c r="AC12" s="5" t="n">
-        <v>45824</v>
+        <v>45825</v>
       </c>
       <c r="AD12" s="8" t="n">
         <v>0.9270833333333334</v>
@@ -10010,7 +10010,7 @@
         </is>
       </c>
       <c r="AJ12" s="5" t="n">
-        <v>45840</v>
+        <v>45841</v>
       </c>
       <c r="AK12" s="8" t="n">
         <v>0.90625</v>
@@ -10042,7 +10042,7 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -10169,7 +10169,7 @@
         </is>
       </c>
       <c r="AC13" s="5" t="n">
-        <v>45846</v>
+        <v>45847</v>
       </c>
       <c r="AD13" s="8" t="n">
         <v>0.84375</v>
@@ -10200,7 +10200,7 @@
         </is>
       </c>
       <c r="AJ13" s="5" t="n">
-        <v>46033</v>
+        <v>46034</v>
       </c>
       <c r="AK13" s="8" t="n">
         <v>0.3958333333333333</v>
@@ -10228,7 +10228,7 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
-        <v>45801</v>
+        <v>45802</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -10355,7 +10355,7 @@
         </is>
       </c>
       <c r="AC14" s="5" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AD14" s="8" t="n">
         <v>0.6458333333333334</v>
@@ -10386,7 +10386,7 @@
         </is>
       </c>
       <c r="AJ14" s="5" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="AK14" s="8" t="n">
         <v>0.8854166666666666</v>
@@ -10414,7 +10414,7 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
-        <v>45699</v>
+        <v>45700</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         </is>
       </c>
       <c r="AC15" s="5" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="AD15" s="8" t="n">
         <v>0.34375</v>
@@ -10572,7 +10572,7 @@
         </is>
       </c>
       <c r="AJ15" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AK15" s="8" t="n">
         <v>0.6458333333333334</v>
@@ -10604,7 +10604,7 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
-        <v>45654</v>
+        <v>45655</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -10736,7 +10736,7 @@
         </is>
       </c>
       <c r="AC16" s="5" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AD16" s="8" t="n">
         <v>0.2604166666666667</v>
@@ -10767,7 +10767,7 @@
         </is>
       </c>
       <c r="AJ16" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AK16" s="8" t="n">
         <v>0.375</v>
@@ -10799,7 +10799,7 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
-        <v>45741</v>
+        <v>45742</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -10927,7 +10927,7 @@
         </is>
       </c>
       <c r="AC17" s="5" t="n">
-        <v>45654</v>
+        <v>45655</v>
       </c>
       <c r="AD17" s="8" t="n">
         <v>0.8541666666666666</v>
@@ -10958,7 +10958,7 @@
         </is>
       </c>
       <c r="AJ17" s="5" t="n">
-        <v>45805</v>
+        <v>45806</v>
       </c>
       <c r="AK17" s="8" t="n">
         <v>0.75</v>
@@ -10986,7 +10986,7 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
         </is>
       </c>
       <c r="AC18" s="5" t="n">
-        <v>45827</v>
+        <v>45828</v>
       </c>
       <c r="AD18" s="8" t="n">
         <v>0.6875</v>
@@ -11144,7 +11144,7 @@
         </is>
       </c>
       <c r="AJ18" s="5" t="n">
-        <v>45989</v>
+        <v>45990</v>
       </c>
       <c r="AK18" s="8" t="n">
         <v>0.6458333333333334</v>
@@ -11172,7 +11172,7 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
-        <v>45814</v>
+        <v>45815</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -11304,7 +11304,7 @@
         </is>
       </c>
       <c r="AC19" s="5" t="n">
-        <v>45799</v>
+        <v>45800</v>
       </c>
       <c r="AD19" s="8" t="n">
         <v>0.9270833333333334</v>
@@ -11335,7 +11335,7 @@
         </is>
       </c>
       <c r="AJ19" s="5" t="n">
-        <v>45821</v>
+        <v>45822</v>
       </c>
       <c r="AK19" s="8" t="n">
         <v>0.9270833333333334</v>
@@ -11367,7 +11367,7 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
-        <v>45751</v>
+        <v>45752</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -11499,7 +11499,7 @@
         </is>
       </c>
       <c r="AC20" s="5" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="AD20" s="8" t="n">
         <v>0.34375</v>
@@ -11530,7 +11530,7 @@
         </is>
       </c>
       <c r="AJ20" s="5" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="AK20" s="8" t="n">
         <v>0.3541666666666667</v>
@@ -11558,7 +11558,7 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
-        <v>45600</v>
+        <v>45601</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         </is>
       </c>
       <c r="AC21" s="5" t="n">
-        <v>45747</v>
+        <v>45748</v>
       </c>
       <c r="AD21" s="8" t="n">
         <v>0.3125</v>
@@ -11721,7 +11721,7 @@
         </is>
       </c>
       <c r="AJ21" s="5" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="AK21" s="8" t="n">
         <v>0.4895833333333333</v>
@@ -11753,7 +11753,7 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -11885,7 +11885,7 @@
         </is>
       </c>
       <c r="AC22" s="5" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AD22" s="8" t="n">
         <v>0.8958333333333334</v>
@@ -11916,7 +11916,7 @@
         </is>
       </c>
       <c r="AJ22" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AK22" s="8" t="n">
         <v>0.84375</v>
@@ -11944,7 +11944,7 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -12076,7 +12076,7 @@
         </is>
       </c>
       <c r="AC23" s="5" t="n">
-        <v>45806</v>
+        <v>45807</v>
       </c>
       <c r="AD23" s="8" t="n">
         <v>0.8333333333333334</v>
@@ -12107,7 +12107,7 @@
         </is>
       </c>
       <c r="AJ23" s="5" t="n">
-        <v>45947</v>
+        <v>45948</v>
       </c>
       <c r="AK23" s="8" t="n">
         <v>0.9479166666666666</v>
@@ -12135,7 +12135,7 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -12267,7 +12267,7 @@
         </is>
       </c>
       <c r="AC24" s="5" t="n">
-        <v>45750</v>
+        <v>45751</v>
       </c>
       <c r="AD24" s="8" t="n">
         <v>0.7083333333333334</v>
@@ -12298,7 +12298,7 @@
         </is>
       </c>
       <c r="AJ24" s="5" t="n">
-        <v>45850</v>
+        <v>45851</v>
       </c>
       <c r="AK24" s="8" t="n">
         <v>0.7291666666666666</v>
@@ -12330,7 +12330,7 @@
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
-        <v>45614</v>
+        <v>45615</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         </is>
       </c>
       <c r="AC25" s="5" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="AD25" s="8" t="n">
         <v>0.6875</v>
@@ -12484,7 +12484,7 @@
         </is>
       </c>
       <c r="AJ25" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AK25" s="8" t="n">
         <v>0.6458333333333334</v>
@@ -12516,7 +12516,7 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
-        <v>45839</v>
+        <v>45840</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -12639,7 +12639,7 @@
         </is>
       </c>
       <c r="AC26" s="5" t="n">
-        <v>45610</v>
+        <v>45611</v>
       </c>
       <c r="AD26" s="8" t="n">
         <v>0.6458333333333334</v>
@@ -12670,7 +12670,7 @@
         </is>
       </c>
       <c r="AJ26" s="5" t="n">
-        <v>45700</v>
+        <v>45701</v>
       </c>
       <c r="AK26" s="8" t="n">
         <v>0.8333333333333334</v>
@@ -12702,7 +12702,7 @@
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -12834,7 +12834,7 @@
         </is>
       </c>
       <c r="AC27" s="5" t="n">
-        <v>45832</v>
+        <v>45833</v>
       </c>
       <c r="AD27" s="8" t="n">
         <v>0.34375</v>
@@ -12865,7 +12865,7 @@
         </is>
       </c>
       <c r="AJ27" s="5" t="n">
-        <v>45896</v>
+        <v>45897</v>
       </c>
       <c r="AK27" s="8" t="n">
         <v>0.375</v>
@@ -12897,7 +12897,7 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -13024,7 +13024,7 @@
         </is>
       </c>
       <c r="AC28" s="5" t="n">
-        <v>45989</v>
+        <v>45990</v>
       </c>
       <c r="AD28" s="8" t="n">
         <v>0.6354166666666666</v>
@@ -13055,7 +13055,7 @@
         </is>
       </c>
       <c r="AJ28" s="5" t="n">
-        <v>46041</v>
+        <v>46042</v>
       </c>
       <c r="AK28" s="8" t="n">
         <v>0.4270833333333333</v>
@@ -13083,7 +13083,7 @@
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
-        <v>45808</v>
+        <v>45809</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         </is>
       </c>
       <c r="AC29" s="5" t="n">
-        <v>45722</v>
+        <v>45723</v>
       </c>
       <c r="AD29" s="8" t="n">
         <v>0.46875</v>
@@ -13246,7 +13246,7 @@
         </is>
       </c>
       <c r="AJ29" s="5" t="n">
-        <v>45800</v>
+        <v>45801</v>
       </c>
       <c r="AK29" s="8" t="n">
         <v>0.46875</v>
@@ -13278,7 +13278,7 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -13405,7 +13405,7 @@
         </is>
       </c>
       <c r="AC30" s="5" t="n">
-        <v>45696</v>
+        <v>45697</v>
       </c>
       <c r="AD30" s="8" t="n">
         <v>0.59375</v>
@@ -13436,7 +13436,7 @@
         </is>
       </c>
       <c r="AJ30" s="5" t="n">
-        <v>45771</v>
+        <v>45772</v>
       </c>
       <c r="AK30" s="8" t="n">
         <v>0.65625</v>
@@ -13468,7 +13468,7 @@
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -13591,7 +13591,7 @@
         </is>
       </c>
       <c r="AC31" s="5" t="n">
-        <v>46033</v>
+        <v>46034</v>
       </c>
       <c r="AD31" s="8" t="n">
         <v>0.4166666666666667</v>
@@ -13622,7 +13622,7 @@
         </is>
       </c>
       <c r="AJ31" s="5" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="AK31" s="8" t="n">
         <v>0.4791666666666667</v>
@@ -13654,7 +13654,7 @@
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
-        <v>45776</v>
+        <v>45777</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -13786,7 +13786,7 @@
         </is>
       </c>
       <c r="AC32" s="5" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="AD32" s="8" t="n">
         <v>0.40625</v>
@@ -13817,7 +13817,7 @@
         </is>
       </c>
       <c r="AJ32" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AK32" s="8" t="n">
         <v>0.75</v>
@@ -13849,7 +13849,7 @@
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -13972,7 +13972,7 @@
         </is>
       </c>
       <c r="AC33" s="5" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="AD33" s="8" t="n">
         <v>0.90625</v>
@@ -14003,7 +14003,7 @@
         </is>
       </c>
       <c r="AJ33" s="5" t="n">
-        <v>45987</v>
+        <v>45988</v>
       </c>
       <c r="AK33" s="8" t="n">
         <v>0.7708333333333334</v>
@@ -16106,7 +16106,8 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Identificador alfanumérico nominal único provincial asignado al NyA para seguimiento resguardando su identidad. En caso de existir.</t>
+          <t>Identificador alfanumérico nominal único provincial asignado al NyA para seguimiento resguardando su identidad. En caso de existir.
+Campo obligatorio.</t>
         </is>
       </c>
     </row>
@@ -16611,7 +16612,11 @@
           <t>ID del Niño, niña o Adolescente</t>
         </is>
       </c>
-      <c r="B54" s="11" t="n"/>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
+          <t>Campo obligatorio.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
